--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\ITMO\Продвинутые методы оптимизации\AOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8EAEEF-7897-439C-9002-5703F2CEE18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,164 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Ты опытный Data Scientist с 10-летним стажем и работаешь в топовой технологической компании уже 10 лет, специализируешься на структурированных данных и градиентном бустинге. Твой код всегда чист, эффективен и соответствует лучшим индустриальным практикам.</t>
+  </si>
+  <si>
+    <t>Ты — трёхкратный Kaggle Grandmaster, выигравший десятки соревнований по табличным данным. Ты мыслишь в терминах быстрых экспериментов, приростов к AUC и «грязных» трюков, но всегда добиваешься максимума на лидерборде.</t>
+  </si>
+  <si>
+    <t>Ты профессор статистики, который обожает математически обосновывать каждое преобразование. Ты склонен проверять гипотезы, смотреть на распределения и применять строгие методы, избегая «хаков», если они не имеют теоретической базы.</t>
+  </si>
+  <si>
+    <t>Ты прагматичный MLOps-инженер и отвечаешь за production-пайплайны. Для тебя важнее всего надежность, воспроизводимость и скорость выполнения. Ты пишешь минималистичный, хорошо структурированный код, избегая нестабильных зависимостей и долгих вычислений.</t>
+  </si>
+  <si>
+    <t>Ты начинающий Junior Data Scientist и всего полгода работаешь в области DS. Ты стараешься следовать учебникам и боишься ошибиться, поэтому твой код прямолинейный, но иногда ты упускаешь важные нюансы или усложняешь простые вещи.</t>
+  </si>
+  <si>
+    <t>Ты Data-инженер, перешедший в ML. До этого ты 15 лет строил ETL-системы, а теперь занялся машинным обучением. Ты смотришь на данные как на конвейер: валидация схемы, обработка аномалий, эффективное использование памяти. Твои решения часто нестандартны, но всегда надёжны.</t>
+  </si>
+  <si>
+    <t>Ты Консультант по машинному обучению из Big4. Ты работаешь в консалтинге и привык быстро разбираться в чужих данных, выдавая работающий прототип за день. Твой код снабжён подробными комментариями для клиента, а все шаги предобработки тщательно обоснованы бизнес-логикой.</t>
+  </si>
+  <si>
+    <t>Ты фанат автоматического машинного обучения и считаешь, что всё должна делать машина. Ты пишешь код так, чтобы его можно было скормить любому датасету, и добавляешь множество автоматических проверок и запасных вариантов обработки.</t>
+  </si>
+  <si>
+    <t>Ты — безэмоциональная машина, генерирующая идеальный инженерный код. Ты выдаёшь решение по стандартному шаблону: загрузка → разметка типов → обработка пропусков → кодирование → сохранение. Ничего лишнего, только документация на уровне docstring.</t>
+  </si>
+  <si>
+    <t>Ты Креативный футурист-изобретатель признаков. Ты обожаешь придумывать новые признаки: взаимодействия, агрегаты, синтетические фичи. Ты готов потратить 90% времени на feature engineering, потому что веришь: данные — это глина, а качество лепки определяет AUC. Твой код может быть неоптимальным, но очень изобретательным.</t>
+  </si>
+  <si>
+    <t>Напиши скрипт предобработки данных.  
+Данные лежат в папке data/. Сохрани обработанные train.csv и test.csv в папку output/.</t>
+  </si>
+  <si>
+    <t>Загрузи train.csv и test.csv, а также все дополнительные таблицы из data/.  
+Объедини их по ключам, которые указаны в описании.  
+Заполни пропуски медианой (числа) и модой (категории).  
+Закодируй все категориальные колонки через Label Encoding.  
+Сохрани результат в output/.</t>
+  </si>
+  <si>
+    <t>Выполни предобработку, дружественную к CatBoost:  
+- Загрузи все таблицы из data/.  
+- Объедини их в один плоский датафрейм, используя связи из описания.  
+- Пропуски заполни медианой / модой.  
+- Категориальные колонки оставь строковыми – CatBoost обработает их сам.  
+- Никакого масштабирования числовых признаков не применяй.  
+- Сохрани train.csv и test.csv в output/.</t>
+  </si>
+  <si>
+    <t>Загрузи все данные.  
+Выполни следующие шаги строго последовательно:  
+1. Удали все строки с выбросами (метод IQR).  
+2. Заполни оставшиеся пропуски средним.  
+3. Примени StandardScaler ко всем числовым колонкам.  
+4. Категориальные колонки закодируй через OneHot Encoding.  
+5. Уменьши размерность через PCA (50 компонент).  
+6. Объедини train и test, выполни PCA на объединённых данных, потом раздели обратно.  
+Сохрани результат.</t>
+  </si>
+  <si>
+    <t>Сфокусируйся на создании признаков.  
+- Из всех временных колонок извлеки год, месяц, день, день недели, час.  
+- Создай агрегаты по группам (среднее, сумма, количество) по ключевым идентификаторам, используя только train-период.  
+- Добавь признаки взаимодействия (произведение, частное) для трёх самых важных числовых пар (выбери их по корреляции).  
+- Не удаляй исходные колонки.  
+- Категориальные признаки оставь строковыми.  
+Сохрани итоговые таблицы.</t>
+  </si>
+  <si>
+    <t>Используй подход, оптимальный для CatBoost с параметрами по умолчанию:  
+- Загрузи train.csv, test.csv и связанные таблицы.  
+- Выполни JOIN'ы строго по описанным в схеме ключам.  
+- Пропуски в числовых колонках замени на медиану, в категориальных — на отдельную строку 'missing'.  
+- Категориальные колонки оставь в строковом типе (не применяй Label/OneHot).  
+- Не масштабируй и не нормализовывай числовые признаки.  
+- Убедись, что при создании агрегатов используются данные только из тренировочного периода (без целевой переменной).  
+Результат сохрани в output/.</t>
+  </si>
+  <si>
+    <t>В папке data/ лежат несколько CSV-файлов, включая train.csv и test.csv.  
+Тебе дано только устное описание связей между таблицами (пользователь передаст его отдельно).  
+Самостоятельно интерпретируй, по каким колонкам нужно джойнить таблицы.  
+Напиши код, который создаёт единый датасет для обучения.  
+Заполни пропуски.  
+Сохрани результат.</t>
+  </si>
+  <si>
+    <t>Загрузи train.csv и test.csv, объедини их в один датафрейм.  
+Обработай пропуски (медиана / мода) и выбросы (Z-score &gt; 3 удалить) на всём датасете.  
+Затем раздели обратно на train и test по исходному размеру.  
+Никакие дополнительные таблицы не используй.  
+Сохрани.</t>
+  </si>
+  <si>
+    <t>Сделай следущее:  
+- Заджойни все таблицы.  
+- Создай лаги и кумулятивные суммы по времени (если есть временная метка).  
+- Посчитай частоту событий за последние 7 и 30 дней.  
+- Обучи предварительный LightGBM, получи важность признаков, удали признаки с нулевой важностью (сохрани отбор только на train).  
+- Оставшиеся категориальные колонки пометь как категории для CatBoost.  
+- Сохрани обработанные train.csv и test.csv.</t>
+  </si>
+  <si>
+    <t>Ты – эксперт, который адаптирует обработку под конкретную схему.
+Проанализируй описание таблиц, полученное от пользователя:
+- Определи основную таблицу и связанные сущности.
+- Категориальные признаки оставь строками, числовые пропуски заполни медианой по группам (если возможно) или словом 'unknown'.
+- Не применяй масштабирование и не удаляй выбросы.
+Сохрани результат.</t>
+  </si>
+  <si>
+    <t>instruct</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>constraints</t>
+  </si>
+  <si>
+    <t>Используй только информацию, явно указанную в описании данных. Не делай предположений о столбцах, которые не описаны пользователем.</t>
+  </si>
+  <si>
+    <t>Отдавай приоритет стабильности и воспроизводимости, а не агрессивным эвристикам. Любое преобразование должно быть безопасным для разных таблиц и запусков.</t>
+  </si>
+  <si>
+    <t>Используй только самые необходимые преобразования. Не добавляй лишний feature engineering, если он не дает явного и универсального преимущества.</t>
+  </si>
+  <si>
+    <t>Выбирай такие преобразования, которые с наибольшей вероятностью улучшат ROC-AUC на табличных данных, даже если скрипт станет сложнее.</t>
+  </si>
+  <si>
+    <t>Полностью исключай утечку таргета и любые преобразования, которые могут использовать информацию из test или из будущих объектов.</t>
+  </si>
+  <si>
+    <t>Строй решение так, чтобы оно работало на разных реляционных схемах без ручной подстройки под конкретный датасет.</t>
+  </si>
+  <si>
+    <t>Все преобразования должны сохранять пригодность данных для CatBoost на стандартных параметрах без дополнительных ручных исправлений после запуска скрипта.</t>
+  </si>
+  <si>
+    <t>Особое внимание уделяй пропускам, типам данных, дубликатам и смешанным признакам. Не допускай падений скрипта из-за неожиданных значений.</t>
+  </si>
+  <si>
+    <t>Предпочитай преобразования, которые легко объяснить и проверить вручную. Избегай слишком сложных или непрозрачных трансформаций.</t>
+  </si>
+  <si>
+    <t>Не используй чрезмерно тяжелые операции. Предобработка должна быть достаточно быстрой, чтобы подходить для многократного запуска в цикле оптимизации.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,11 +211,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +496,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.77734375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\ITMO\Продвинутые методы оптимизации\AOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8EAEEF-7897-439C-9002-5703F2CEE18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE83932-7731-4607-AF27-9772E34B8366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,88 +57,6 @@
     <t>Ты Креативный футурист-изобретатель признаков. Ты обожаешь придумывать новые признаки: взаимодействия, агрегаты, синтетические фичи. Ты готов потратить 90% времени на feature engineering, потому что веришь: данные — это глина, а качество лепки определяет AUC. Твой код может быть неоптимальным, но очень изобретательным.</t>
   </si>
   <si>
-    <t>Напиши скрипт предобработки данных.  
-Данные лежат в папке data/. Сохрани обработанные train.csv и test.csv в папку output/.</t>
-  </si>
-  <si>
-    <t>Загрузи train.csv и test.csv, а также все дополнительные таблицы из data/.  
-Объедини их по ключам, которые указаны в описании.  
-Заполни пропуски медианой (числа) и модой (категории).  
-Закодируй все категориальные колонки через Label Encoding.  
-Сохрани результат в output/.</t>
-  </si>
-  <si>
-    <t>Выполни предобработку, дружественную к CatBoost:  
-- Загрузи все таблицы из data/.  
-- Объедини их в один плоский датафрейм, используя связи из описания.  
-- Пропуски заполни медианой / модой.  
-- Категориальные колонки оставь строковыми – CatBoost обработает их сам.  
-- Никакого масштабирования числовых признаков не применяй.  
-- Сохрани train.csv и test.csv в output/.</t>
-  </si>
-  <si>
-    <t>Загрузи все данные.  
-Выполни следующие шаги строго последовательно:  
-1. Удали все строки с выбросами (метод IQR).  
-2. Заполни оставшиеся пропуски средним.  
-3. Примени StandardScaler ко всем числовым колонкам.  
-4. Категориальные колонки закодируй через OneHot Encoding.  
-5. Уменьши размерность через PCA (50 компонент).  
-6. Объедини train и test, выполни PCA на объединённых данных, потом раздели обратно.  
-Сохрани результат.</t>
-  </si>
-  <si>
-    <t>Сфокусируйся на создании признаков.  
-- Из всех временных колонок извлеки год, месяц, день, день недели, час.  
-- Создай агрегаты по группам (среднее, сумма, количество) по ключевым идентификаторам, используя только train-период.  
-- Добавь признаки взаимодействия (произведение, частное) для трёх самых важных числовых пар (выбери их по корреляции).  
-- Не удаляй исходные колонки.  
-- Категориальные признаки оставь строковыми.  
-Сохрани итоговые таблицы.</t>
-  </si>
-  <si>
-    <t>Используй подход, оптимальный для CatBoost с параметрами по умолчанию:  
-- Загрузи train.csv, test.csv и связанные таблицы.  
-- Выполни JOIN'ы строго по описанным в схеме ключам.  
-- Пропуски в числовых колонках замени на медиану, в категориальных — на отдельную строку 'missing'.  
-- Категориальные колонки оставь в строковом типе (не применяй Label/OneHot).  
-- Не масштабируй и не нормализовывай числовые признаки.  
-- Убедись, что при создании агрегатов используются данные только из тренировочного периода (без целевой переменной).  
-Результат сохрани в output/.</t>
-  </si>
-  <si>
-    <t>В папке data/ лежат несколько CSV-файлов, включая train.csv и test.csv.  
-Тебе дано только устное описание связей между таблицами (пользователь передаст его отдельно).  
-Самостоятельно интерпретируй, по каким колонкам нужно джойнить таблицы.  
-Напиши код, который создаёт единый датасет для обучения.  
-Заполни пропуски.  
-Сохрани результат.</t>
-  </si>
-  <si>
-    <t>Загрузи train.csv и test.csv, объедини их в один датафрейм.  
-Обработай пропуски (медиана / мода) и выбросы (Z-score &gt; 3 удалить) на всём датасете.  
-Затем раздели обратно на train и test по исходному размеру.  
-Никакие дополнительные таблицы не используй.  
-Сохрани.</t>
-  </si>
-  <si>
-    <t>Сделай следущее:  
-- Заджойни все таблицы.  
-- Создай лаги и кумулятивные суммы по времени (если есть временная метка).  
-- Посчитай частоту событий за последние 7 и 30 дней.  
-- Обучи предварительный LightGBM, получи важность признаков, удали признаки с нулевой важностью (сохрани отбор только на train).  
-- Оставшиеся категориальные колонки пометь как категории для CatBoost.  
-- Сохрани обработанные train.csv и test.csv.</t>
-  </si>
-  <si>
-    <t>Ты – эксперт, который адаптирует обработку под конкретную схему.
-Проанализируй описание таблиц, полученное от пользователя:
-- Определи основную таблицу и связанные сущности.
-- Категориальные признаки оставь строками, числовые пропуски заполни медианой по группам (если возможно) или словом 'unknown'.
-- Не применяй масштабирование и не удаляй выбросы.
-Сохрани результат.</t>
-  </si>
-  <si>
     <t>instruct</t>
   </si>
   <si>
@@ -148,34 +66,64 @@
     <t>constraints</t>
   </si>
   <si>
-    <t>Используй только информацию, явно указанную в описании данных. Не делай предположений о столбцах, которые не описаны пользователем.</t>
-  </si>
-  <si>
-    <t>Отдавай приоритет стабильности и воспроизводимости, а не агрессивным эвристикам. Любое преобразование должно быть безопасным для разных таблиц и запусков.</t>
-  </si>
-  <si>
-    <t>Используй только самые необходимые преобразования. Не добавляй лишний feature engineering, если он не дает явного и универсального преимущества.</t>
-  </si>
-  <si>
-    <t>Выбирай такие преобразования, которые с наибольшей вероятностью улучшат ROC-AUC на табличных данных, даже если скрипт станет сложнее.</t>
-  </si>
-  <si>
-    <t>Полностью исключай утечку таргета и любые преобразования, которые могут использовать информацию из test или из будущих объектов.</t>
-  </si>
-  <si>
-    <t>Строй решение так, чтобы оно работало на разных реляционных схемах без ручной подстройки под конкретный датасет.</t>
-  </si>
-  <si>
-    <t>Все преобразования должны сохранять пригодность данных для CatBoost на стандартных параметрах без дополнительных ручных исправлений после запуска скрипта.</t>
-  </si>
-  <si>
-    <t>Особое внимание уделяй пропускам, типам данных, дубликатам и смешанным признакам. Не допускай падений скрипта из-за неожиданных значений.</t>
-  </si>
-  <si>
-    <t>Предпочитай преобразования, которые легко объяснить и проверить вручную. Избегай слишком сложных или непрозрачных трансформаций.</t>
-  </si>
-  <si>
-    <t>Не используй чрезмерно тяжелые операции. Предобработка должна быть достаточно быстрой, чтобы подходить для многократного запуска в цикле оптимизации.</t>
+    <t>Загрузи все CSV‑файлы из папки data/, исключая readme.txt если есть. Выполни inner join вспомогательных таблиц к train.csv и отдельно к test.csv по всем общим колонкам. Удали строки с пропусками в целевой переменной и полные дубликаты строк. Не производи никаких других преобразований. Сохрани итоговые таблицы как output/train.csv и output/test.csv. Верни только Python‑код, без комментариев и без текста вне кода.</t>
+  </si>
+  <si>
+    <t>Прочитай все CSV в data/. Объедини вспомогательные таблицы с train.csv и test.csv через inner join. Удали колонки, в которых более 50 % пропусков. Числовые пропуски заполни медианой, вычисленной на train; категориальные — строкой 'missing'. Все категориальные колонки закодируй целочисленными метками (label encoding) по уникальным значениям из train. Сохрани результат в output/train.csv и output/test.csv. Выведи строго Python‑код без комментариев.</t>
+  </si>
+  <si>
+    <t>Загрузи данные из data/. Выполни inner join вспомогательных таблиц к train.csv и test.csv. Удали колонки с более чем 30 % пропусков. Удали константные колонки. Из каждой пары числовых колонок с корреляцией Пирсона выше 0.95 удали одну. Оставшиеся пропуски заполни 0. Сохрани итог в output/train.csv и output/test.csv. Только код, без комментариев.</t>
+  </si>
+  <si>
+    <t>Прочитай CSV из data/. Выполни inner join вспомогательных таблиц к train.csv и test.csv. Для каждой пары числовых колонок создай признаки: сумму, разность и произведение. Исходные числовые колонки с долей пропусков &gt;5 % удали. Все оставшиеся пропуски заполни 0. Сохрани результат в output/train.csv и output/test.csv. Верни только Python‑код без комментариев.</t>
+  </si>
+  <si>
+    <t>Загрузи таблицы из data/. Объедини через inner join с train.csv и test.csv. Удали все числовые колонки, кроме целевой. Для категориальных с более чем 10 уникальными значениями примени count encoding (частоту появления из train). Для остальных категориальных используй One‑Hot encoding (оставь топ‑50 по частоте значений, остальное в 'other'). Сохрани итог в output/train.csv и output/test.csv. Выведи только Python‑код без комментариев.</t>
+  </si>
+  <si>
+    <t>Прочитай CSV в data/. Соедини таблицы через inner join с train.csv и test.csv. Оставь только числовые колонки (включая целевую). Пропуски заполни медианой по train. Ограничь выбросы: значения за пределами [Q1 - 1.5·IQR, Q3 + 1.5·IQR] приведи к ближайшей границе. Примени RobustScaler. Сохрани в output/train.csv и output/test.csv. Только код без комментариев.</t>
+  </si>
+  <si>
+    <t>Загрузи все CSV из data/. Выполни inner join к train.csv и test.csv. Для каждой категориальной колонки создай числовые агрегаты: среднее и стандартное отклонение каждой числовой колонки внутри группы (по train). Замени исходные категориальные колонки на эти агрегаты, исходные числовые оставь без изменений. Пропуски в новых агрегатных признаках заполни 0. Сохрани в output/train.csv и output/test.csv. Верни только Python‑код без комментариев.</t>
+  </si>
+  <si>
+    <t>Загрузи данные из data/. Объедини через inner join с train.csv и test.csv. Для каждой колонки, содержащей пропуски, добавь бинарную колонку‑индикатор (_isna). Числовые пропуски заполни средним, категориальные — самым частым значением (модой) из train. Категориальные признаки закодируй pd.factorize. Не удаляй оригинальные колонки. Сохрани в output/train.csv и output/test.csv. Только код без комментариев.</t>
+  </si>
+  <si>
+    <t>Прочитай CSV в data/. Выполни inner join вспомогательных таблиц к train.csv и test.csv. Все категориальные признаки замени на их частоту в train (count encoding). Удали числовые колонки, у которых по модулю корреляция с целевой на train меньше 0.01. Удали категориальные с 1 уникальным значением. Пропуски заполни 0. Сохрани в output/train.csv и output/test.csv. Только Python‑код, без комментариев.</t>
+  </si>
+  <si>
+    <t>Загрузи таблицы из data/. Выполни inner join к train.csv и test.csv. Не удаляй колонки. Числовые пропуски заполни константой -999, категориальные — строкой 'unknown'. Все категориальные закодируй через pd.factorize (label encoding). Добавь признак row_missing_count — общее число пропусков в строке. Сохрани в output/train.csv и output/test.csv. Верни только Python‑код без комментариев.</t>
+  </si>
+  <si>
+    <t>Используй только стандартные библиотеки pandas, numpy и sklearn; внешние API, сетевые запросы и пакеты, требующие отдельной установки, недопустимы.</t>
+  </si>
+  <si>
+    <t>Не изменяй имена файлов и ожидаемую структуру папок: читай данные только из data/, сохраняй результат строго в output/train.csv и output/test.csv.</t>
+  </si>
+  <si>
+    <t>Любые статистики для импутации, кодирования или масштабирования вычисляй исключительно на train.csv; к test.csv применяй только уже зафиксированные на train значения.</t>
+  </si>
+  <si>
+    <t>Не включай в код обучение моделей, валидацию, подбор гиперпараметров, кросс-валидацию, визуализацию или разведочный анализ с выводом результатов.</t>
+  </si>
+  <si>
+    <t>Не изменяй значения целевой переменной, а также порядок строк и индексы исходных train.csv/test.csv в итоговых файлах.</t>
+  </si>
+  <si>
+    <t>Код должен быть полностью самодостаточным: запускается как скрипт без аргументов командной строки, без интерактивного ввода и без ожидания действий пользователя.</t>
+  </si>
+  <si>
+    <t>Не используй конструкции try/except для подавления ошибок чтения файлов, отсутствия колонок или несовпадения схем данных; при некорректных входных данных скрипт должен завершаться с исключением.</t>
+  </si>
+  <si>
+    <t>Не выводи в stdout никакой текстовой информации, диагностики, прогресса или предупреждений; допускается только запись результирующих файлов на диск.</t>
+  </si>
+  <si>
+    <t>Не используй случайность без явно заданного random_state во всех операциях, где она применяется.</t>
+  </si>
+  <si>
+    <t>Гарантируй, что финальные output/train.csv и output/test.csv содержат идентичный набор признаковых колонок (за исключением целевой переменной), чтобы обеспечить совместимость с последующим обучением.</t>
   </si>
 </sst>
 </file>
@@ -507,13 +455,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -521,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
@@ -532,7 +480,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>24</v>
@@ -543,7 +491,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>25</v>
@@ -554,7 +502,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>26</v>
@@ -598,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>30</v>
@@ -609,7 +557,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>31</v>
@@ -620,7 +568,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>

--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\ITMO\Продвинутые методы оптимизации\AOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE83932-7731-4607-AF27-9772E34B8366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5327202A-5152-4FAB-B0EF-F70DCF155E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,49 +81,49 @@
     <t>Загрузи таблицы из data/. Объедини через inner join с train.csv и test.csv. Удали все числовые колонки, кроме целевой. Для категориальных с более чем 10 уникальными значениями примени count encoding (частоту появления из train). Для остальных категориальных используй One‑Hot encoding (оставь топ‑50 по частоте значений, остальное в 'other'). Сохрани итог в output/train.csv и output/test.csv. Выведи только Python‑код без комментариев.</t>
   </si>
   <si>
-    <t>Прочитай CSV в data/. Соедини таблицы через inner join с train.csv и test.csv. Оставь только числовые колонки (включая целевую). Пропуски заполни медианой по train. Ограничь выбросы: значения за пределами [Q1 - 1.5·IQR, Q3 + 1.5·IQR] приведи к ближайшей границе. Примени RobustScaler. Сохрани в output/train.csv и output/test.csv. Только код без комментариев.</t>
-  </si>
-  <si>
     <t>Загрузи все CSV из data/. Выполни inner join к train.csv и test.csv. Для каждой категориальной колонки создай числовые агрегаты: среднее и стандартное отклонение каждой числовой колонки внутри группы (по train). Замени исходные категориальные колонки на эти агрегаты, исходные числовые оставь без изменений. Пропуски в новых агрегатных признаках заполни 0. Сохрани в output/train.csv и output/test.csv. Верни только Python‑код без комментариев.</t>
   </si>
   <si>
-    <t>Загрузи данные из data/. Объедини через inner join с train.csv и test.csv. Для каждой колонки, содержащей пропуски, добавь бинарную колонку‑индикатор (_isna). Числовые пропуски заполни средним, категориальные — самым частым значением (модой) из train. Категориальные признаки закодируй pd.factorize. Не удаляй оригинальные колонки. Сохрани в output/train.csv и output/test.csv. Только код без комментариев.</t>
-  </si>
-  <si>
     <t>Прочитай CSV в data/. Выполни inner join вспомогательных таблиц к train.csv и test.csv. Все категориальные признаки замени на их частоту в train (count encoding). Удали числовые колонки, у которых по модулю корреляция с целевой на train меньше 0.01. Удали категориальные с 1 уникальным значением. Пропуски заполни 0. Сохрани в output/train.csv и output/test.csv. Только Python‑код, без комментариев.</t>
   </si>
   <si>
-    <t>Загрузи таблицы из data/. Выполни inner join к train.csv и test.csv. Не удаляй колонки. Числовые пропуски заполни константой -999, категориальные — строкой 'unknown'. Все категориальные закодируй через pd.factorize (label encoding). Добавь признак row_missing_count — общее число пропусков в строке. Сохрани в output/train.csv и output/test.csv. Верни только Python‑код без комментариев.</t>
-  </si>
-  <si>
-    <t>Используй только стандартные библиотеки pandas, numpy и sklearn; внешние API, сетевые запросы и пакеты, требующие отдельной установки, недопустимы.</t>
-  </si>
-  <si>
-    <t>Не изменяй имена файлов и ожидаемую структуру папок: читай данные только из data/, сохраняй результат строго в output/train.csv и output/test.csv.</t>
-  </si>
-  <si>
-    <t>Любые статистики для импутации, кодирования или масштабирования вычисляй исключительно на train.csv; к test.csv применяй только уже зафиксированные на train значения.</t>
-  </si>
-  <si>
-    <t>Не включай в код обучение моделей, валидацию, подбор гиперпараметров, кросс-валидацию, визуализацию или разведочный анализ с выводом результатов.</t>
-  </si>
-  <si>
-    <t>Не изменяй значения целевой переменной, а также порядок строк и индексы исходных train.csv/test.csv в итоговых файлах.</t>
-  </si>
-  <si>
-    <t>Код должен быть полностью самодостаточным: запускается как скрипт без аргументов командной строки, без интерактивного ввода и без ожидания действий пользователя.</t>
-  </si>
-  <si>
-    <t>Не используй конструкции try/except для подавления ошибок чтения файлов, отсутствия колонок или несовпадения схем данных; при некорректных входных данных скрипт должен завершаться с исключением.</t>
-  </si>
-  <si>
-    <t>Не выводи в stdout никакой текстовой информации, диагностики, прогресса или предупреждений; допускается только запись результирующих файлов на диск.</t>
-  </si>
-  <si>
-    <t>Не используй случайность без явно заданного random_state во всех операциях, где она применяется.</t>
-  </si>
-  <si>
-    <t>Гарантируй, что финальные output/train.csv и output/test.csv содержат идентичный набор признаковых колонок (за исключением целевой переменной), чтобы обеспечить совместимость с последующим обучением.</t>
+    <t>Используй только стандартные библиотеки pandas, numpy и sklearn; внешние API, сетевые запросы и пакеты, требующие отдельной установки, недопустимы. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Не изменяй имена файлов и ожидаемую структуру папок: читай данные только из data/, сохраняй результат строго в output/train.csv и output/test.csv. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Любые статистики для импутации, кодирования или масштабирования вычисляй исключительно на train.csv; к test.csv применяй только уже зафиксированные на train значения. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Не включай в код обучение моделей, валидацию, подбор гиперпараметров, кросс-валидацию, визуализацию или разведочный анализ с выводом результатов. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Код должен быть полностью самодостаточным: запускается как скрипт без аргументов командной строки, без интерактивного ввода и без ожидания действий пользователя. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Не используй конструкции try/except для подавления ошибок чтения файлов, отсутствия колонок или несовпадения схем данных; при некорректных входных данных скрипт должен завершаться с исключением. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Не выводи в stdout никакой текстовой информации, диагностики, прогресса или предупреждений; допускается только запись результирующих файлов на диск. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Не используй случайность без явно заданного random_state во всех операциях, где она применяется. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Гарантируй, что финальные output/train.csv и output/test.csv содержат идентичный набор признаковых колонок (за исключением целевой переменной), чтобы обеспечить совместимость с последующим обучением. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не изменяй значения целевой переменной, а также порядок строк и индексы исходных train.csv/test.csv в итоговых файлах. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось. </t>
+  </si>
+  <si>
+    <t>Загрузи данные из data/. Объедини через inner join с train.csv и test.csv. Для каждой колонки, содержащей пропуски, добавь бинарную колонку‑индикатор (_isna). Числовые пропуски заполни средним, категориальные — самым частым значением (модой) из train. Категориальные признаки закодируй pd.factorize. Удали неинформативные колонки, которые обозначают индекс. Сохрани в output/train.csv и output/test.csv. Только код без комментариев.</t>
+  </si>
+  <si>
+    <t>Прочитай CSV в data/. Соедини таблицы через inner join с train.csv и test.csv. Оставь только числовые колонки (включая целевую). Пропуски заполни медианой по train. Ограничь выбросы: значения за пределами [Q1 - 1.5·IQR, Q3 + 1.5·IQR] приведи к ближайшей границе. Примени RobustScaler. Удали неинформативные колонки, которые обозначают индекс. Сохрани в output/train.csv и output/test.csv. Только код без комментариев.</t>
+  </si>
+  <si>
+    <t>Загрузи таблицы из data/. Выполни inner join к train.csv и test.csv. Не удаляй колонки. Числовые пропуски заполни константой -999, категориальные — строкой 'unknown'. Все категориальные закодируй через pd.factorize (label encoding). Добавь признак row_missing_count — общее число пропусков в строке. Удали неинформативные колонки, которые обозначают индекс. Сохрани в output/train.csv и output/test.csv. Верни только Python‑код без комментариев.</t>
   </si>
 </sst>
 </file>
@@ -162,9 +162,11 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -464,7 +466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,10 +474,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -483,10 +485,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -494,10 +496,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -505,10 +507,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -516,62 +518,62 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\ITMO\Продвинутые методы оптимизации\AOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5327202A-5152-4FAB-B0EF-F70DCF155E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A94CD-73A2-440D-9959-21114C970BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,30 +93,9 @@
     <t>Не изменяй имена файлов и ожидаемую структуру папок: читай данные только из data/, сохраняй результат строго в output/train.csv и output/test.csv. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
   </si>
   <si>
-    <t>Любые статистики для импутации, кодирования или масштабирования вычисляй исключительно на train.csv; к test.csv применяй только уже зафиксированные на train значения. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
-  </si>
-  <si>
-    <t>Не включай в код обучение моделей, валидацию, подбор гиперпараметров, кросс-валидацию, визуализацию или разведочный анализ с выводом результатов. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
-  </si>
-  <si>
-    <t>Код должен быть полностью самодостаточным: запускается как скрипт без аргументов командной строки, без интерактивного ввода и без ожидания действий пользователя. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
-  </si>
-  <si>
-    <t>Не используй конструкции try/except для подавления ошибок чтения файлов, отсутствия колонок или несовпадения схем данных; при некорректных входных данных скрипт должен завершаться с исключением. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
-  </si>
-  <si>
     <t>Не выводи в stdout никакой текстовой информации, диагностики, прогресса или предупреждений; допускается только запись результирующих файлов на диск. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
   </si>
   <si>
-    <t>Не используй случайность без явно заданного random_state во всех операциях, где она применяется. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
-  </si>
-  <si>
-    <t>Гарантируй, что финальные output/train.csv и output/test.csv содержат идентичный набор признаковых колонок (за исключением целевой переменной), чтобы обеспечить совместимость с последующим обучением. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Не изменяй значения целевой переменной, а также порядок строк и индексы исходных train.csv/test.csv в итоговых файлах. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, важно чтобы количество строк исходных train.csv и test.csv не изменилось. </t>
-  </si>
-  <si>
     <t>Загрузи данные из data/. Объедини через inner join с train.csv и test.csv. Для каждой колонки, содержащей пропуски, добавь бинарную колонку‑индикатор (_isna). Числовые пропуски заполни средним, категориальные — самым частым значением (модой) из train. Категориальные признаки закодируй pd.factorize. Удали неинформативные колонки, которые обозначают индекс. Сохрани в output/train.csv и output/test.csv. Только код без комментариев.</t>
   </si>
   <si>
@@ -124,6 +103,27 @@
   </si>
   <si>
     <t>Загрузи таблицы из data/. Выполни inner join к train.csv и test.csv. Не удаляй колонки. Числовые пропуски заполни константой -999, категориальные — строкой 'unknown'. Все категориальные закодируй через pd.factorize (label encoding). Добавь признак row_missing_count — общее число пропусков в строке. Удали неинформативные колонки, которые обозначают индекс. Сохрани в output/train.csv и output/test.csv. Верни только Python‑код без комментариев.</t>
+  </si>
+  <si>
+    <t>Не используй случайность без явно заданного random_state во всех операциях, где она применяется. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных.</t>
+  </si>
+  <si>
+    <t>Гарантируй, что финальные output/train.csv и output/test.csv содержат идентичный набор признаковых колонок (за исключением целевой переменной), чтобы обеспечить совместимость с последующим обучением. При объедиении таблиц используй только inner соединение.</t>
+  </si>
+  <si>
+    <t>Любые статистики для импутации, кодирования или масштабирования вычисляй исключительно на train.csv; к test.csv применяй только уже зафиксированные на train значения. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Не включай в код обучение моделей, валидацию, подбор гиперпараметров, кросс-валидацию, визуализацию или разведочный анализ с выводом результатов. При объедиении таблиц используй только inner соединение.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не изменяй значения целевой переменной, а также порядок строк и индексы исходных train.csv/test.csv в итоговых файлах. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, чтобы количество строк исходных train.csv и test.csv не изменилось. </t>
+  </si>
+  <si>
+    <t>Код должен быть полностью самодостаточным: запускается как скрипт без аргументов командной строки, без интерактивного ввода и без ожидания действий пользователя. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
+  </si>
+  <si>
+    <t>Не используй конструкции try/except для подавления ошибок чтения файлов, отсутствия колонок или несовпадения схем данных; при некорректных входных данных скрипт должен завершаться с исключением. При объедиении таблиц используй только inner соединение, иначе очень сильно взрывается размерность данных, проследи за тем, чтобы количество строк исходных train.csv и test.csv не изменилось.</t>
   </si>
 </sst>
 </file>
@@ -496,7 +496,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="144" x14ac:dyDescent="0.3">
@@ -507,7 +507,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
@@ -518,7 +518,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
@@ -526,10 +526,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
@@ -540,7 +540,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
@@ -548,10 +548,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
@@ -562,7 +562,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
@@ -570,10 +570,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\ITMO\Продвинутые методы оптимизации\AOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A94CD-73A2-440D-9959-21114C970BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F40D80-FD17-4BCD-A63C-3E2C20B31069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/prompts.xlsx
+++ b/prompts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\ITMO\Продвинутые методы оптимизации\AOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F40D80-FD17-4BCD-A63C-3E2C20B31069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C497D7D-814F-45CC-BB4C-CA1E1C133012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
